--- a/extraction_script/data/تاييديه_اعتبارات_هزينه_اي_،_اختصاصي_،_تملک_سال_98.xlsx
+++ b/extraction_script/data/تاييديه_اعتبارات_هزينه_اي_،_اختصاصي_،_تملک_سال_98.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin KHoojavi\Downloads\persian-smart-accounting\extraction_script\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Armin KHoojavi\Downloads\persian-smart-accounting1\extraction_script\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33E6DA3-932D-4327-A0CF-327FD81D1C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A9FEF4F-1F60-4740-88C8-4198409D5E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13035" yWindow="4455" windowWidth="15375" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="15375" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="تاییدیه مصارف اداره کل خزانه" sheetId="1" r:id="rId1"/>
+    <sheet name="تا" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1403,6 +1403,13 @@
     <mergeCell ref="D29:H29"/>
     <mergeCell ref="D5:H5"/>
     <mergeCell ref="D23:H23"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="D34:H34"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D44:H44"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="C19:H19"/>
@@ -1419,7 +1426,6 @@
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="D15:H15"/>
-    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="B48:B49"/>
     <mergeCell ref="D11:H11"/>
@@ -1428,8 +1434,6 @@
     <mergeCell ref="D41:H41"/>
     <mergeCell ref="D32:H32"/>
     <mergeCell ref="D17:H17"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="C6:H6"/>
     <mergeCell ref="D30:H30"/>
     <mergeCell ref="D39:H39"/>
     <mergeCell ref="D48:G48"/>
@@ -1438,10 +1442,6 @@
     <mergeCell ref="D35:H35"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D34:H34"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="D31:H31"/>
-    <mergeCell ref="D44:H44"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="D40:H40"/>
     <mergeCell ref="D36:H36"/>
